--- a/www/download/IND.gross_output.s.us.EXI382.xlsx
+++ b/www/download/IND.gross_output.s.us.EXI382.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,144 +688,144 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>642849.110429386</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>735484.990365204</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.749</t>
+          <t>830650.841650739</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.664</t>
+          <t>737218.495798289</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.782</t>
+          <t>867262.486498437</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.875</t>
+          <t>971243.02212609</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>940205.341157796</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>996325.106259982</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1051828.92989796</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>1.058</t>
+          <t>1174263.92698113</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1319988.0312954</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>1.265</t>
+          <t>1403514.38552445</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>1.379</t>
+          <t>1529832.72507312</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>1.385</t>
+          <t>1537144.38342525</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>1.397</t>
+          <t>1549717.29408319</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1.855</t>
+          <t>2058210.79941558</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2.103</t>
+          <t>2333689.00687643</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2.329</t>
+          <t>2584239.25020315</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>2430072.77168522</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.067</t>
+          <t>2293102.01838561</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.117</t>
+          <t>2348828.7313627</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>2468703.66328835</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2.365</t>
+          <t>2624120.56835423</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>2.324</t>
+          <t>2578406.83718431</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.311</t>
+          <t>2564235.90609036</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2.332</t>
+          <t>2587116.75928971</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>2.434</t>
+          <t>2700094.0032167</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -830,144 +835,144 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>391020.908102254</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>403700.145406576</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>408747.379142458</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>429187.186702247</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.343</t>
+          <t>448819.814674426</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.365</t>
+          <t>477517.781937716</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>505401.949213838</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>519300.641096725</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.413</t>
+          <t>540595.744103906</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>562753.847825713</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.461</t>
+          <t>603593.701192323</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>0.496</t>
+          <t>648275.277486624</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.526</t>
+          <t>687956.488101835</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.553</t>
+          <t>723748.651390222</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.523</t>
+          <t>683703.678855762</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>726052.591077183</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>0.591</t>
+          <t>772965.798284599</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>0.609</t>
+          <t>797176.098793183</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>808311.024420961</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.633</t>
+          <t>828402.032472174</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>860314.821061565</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>0.678</t>
+          <t>887079.352557232</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.713</t>
+          <t>931975.633503074</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>980520.984029278</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.773</t>
+          <t>1010749.93740505</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>0.786</t>
+          <t>1028216.33809791</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>1043811.73098384</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -977,144 +982,144 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>541281.637415645</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>549377.156701978</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.436</t>
+          <t>565606.166957802</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>584172.121840974</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.482</t>
+          <t>625426.181230976</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.525</t>
+          <t>681964.910268392</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.543</t>
+          <t>704730.061919015</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.548</t>
+          <t>711235.859337099</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>716145.527920787</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>752539.601914946</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.617</t>
+          <t>800051.275246721</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>855685.316430245</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.701</t>
+          <t>909410.959564939</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.718</t>
+          <t>931953.537321194</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>871549.842671067</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.736</t>
+          <t>954339.827259172</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>0.792</t>
+          <t>1027453.00748118</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>1052720.52674548</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.821</t>
+          <t>1064186.37229802</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>1079554.26433908</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.861</t>
+          <t>1117252.90688823</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>0.887</t>
+          <t>1149979.02456019</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>1200405.99476122</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>1237328.06558221</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.991</t>
+          <t>1285847.6659665</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>1.002</t>
+          <t>1300161.68776288</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1322556.4860493</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1124,144 +1129,144 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33387.2194725734</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>23327.4193130702</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>26774.9782913088</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>33286.7399093646</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>32033.5873647222</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>36023.8725266684</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>40082.5911395038</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>43120.0127263647</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>46911.0185226137</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.043</t>
+          <t>54035.9953206914</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>66215.381638042</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>75665.5277696344</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>90942.4769604698</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>106888.029932355</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.077</t>
+          <t>97564.0930546447</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>99100.5890313891</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>107343.239373393</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.088</t>
+          <t>112114.194796552</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>108211.068869786</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>114363.579815011</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.096</t>
+          <t>121625.857069346</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>127578.161250142</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>139558.393637725</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>146936.398467091</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.124</t>
+          <t>157268.448327749</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>0.13</t>
+          <t>165375.931556104</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.133</t>
+          <t>169115.811890214</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1271,144 +1276,144 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.954</t>
+          <t>1267036.31051026</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>1428630.05252789</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.244</t>
+          <t>1652047.54641086</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.209</t>
+          <t>1605159.64864835</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.918</t>
+          <t>1219767.76969576</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.205</t>
+          <t>1600676.03387012</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1.067</t>
+          <t>1417228.1274433</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.939</t>
+          <t>1247485.55294219</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>0.872</t>
+          <t>1157450.1409717</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>1.007</t>
+          <t>1337502.15615362</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1806744.85066281</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>1.616</t>
+          <t>2146728.8787464</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>1.869</t>
+          <t>2482016.15057104</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>2815588.01518293</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2.155</t>
+          <t>2861931.50348528</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>2.899</t>
+          <t>3849725.66905751</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>3.278</t>
+          <t>4353627.77785888</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>3.345</t>
+          <t>4442133.90022994</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>4317646.36843504</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.211</t>
+          <t>4264885.00324592</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>2.775</t>
+          <t>3685940.41741125</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>2.775</t>
+          <t>3685808.61950663</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>4130991.88975061</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>2.745</t>
+          <t>3645307.67576411</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.813</t>
+          <t>3735418.88773061</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2.868</t>
+          <t>3809190.6250401</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>2.962</t>
+          <t>3934149.52359463</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1418,144 +1423,144 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.852</t>
+          <t>1094567.24887789</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>1196368.71342961</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.081</t>
+          <t>1388512.44522066</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.057</t>
+          <t>1358549.17437294</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>1.202</t>
+          <t>1544316.3884376</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.539</t>
+          <t>1977133.45667512</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1.572</t>
+          <t>2020023.9471052</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>1.527</t>
+          <t>1962304.62301686</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1919057.82475978</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>1.566</t>
+          <t>2012116.2178132</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>1.785</t>
+          <t>2293867.98404423</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>1.986</t>
+          <t>2551381.91895805</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2.011</t>
+          <t>2583098.12262069</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>1.977</t>
+          <t>2539633.58614257</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>1.833</t>
+          <t>2355505.25582458</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>2.314</t>
+          <t>2972666.02833856</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>2.392</t>
+          <t>3072615.11391828</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>2.709</t>
+          <t>3479961.97793935</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>2.587</t>
+          <t>3324410.63826326</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>3298268.8885471</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>2.583</t>
+          <t>3319076.04235897</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>2.596</t>
+          <t>3334835.82741264</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2.7</t>
+          <t>3469583.23267045</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>3460899.95867919</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.87</t>
+          <t>3687904.38503729</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>3699641.36968888</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>2.972</t>
+          <t>3818266.88721208</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1565,144 +1570,144 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1880349.57084244</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.679</t>
+          <t>2333182.40799051</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2.141</t>
+          <t>2975578.83017826</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.321</t>
+          <t>3225054.20997773</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>2.567</t>
+          <t>3566544.35005527</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>3.368</t>
+          <t>4680094.7290994</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3.841</t>
+          <t>5336663.19876955</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>4.049</t>
+          <t>5625834.00203726</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>3.978</t>
+          <t>5528272.44744305</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>4.285</t>
+          <t>5953597.34395614</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>5.252</t>
+          <t>7298122.35822646</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>6.488</t>
+          <t>9016595.17036277</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>7.769</t>
+          <t>10797386.4434394</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>9.245</t>
+          <t>12842180.7234836</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>10.607</t>
+          <t>14732552.5935627</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>13.487</t>
+          <t>18739753.3018195</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>16.004</t>
+          <t>22236825.7884525</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>19.213</t>
+          <t>26689933.5668059</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>20.788</t>
+          <t>28881540.7531505</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
         <is>
-          <t>22.16</t>
+          <t>30783026.2565354</t>
         </is>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>27.186</t>
+          <t>37759817.8905316</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>27.389</t>
+          <t>38033457.2966507</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>29.346</t>
+          <t>40744701.0236384</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>32.301</t>
+          <t>44852480.40194</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>34.82</t>
+          <t>48352676.6474347</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>37.037</t>
+          <t>51427333.303337</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>39.076</t>
+          <t>54258844.7977629</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1712,144 +1717,144 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>13904.6785779279</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>15187.061840926</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16024.3725688523</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>17090.1746717973</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>18589.3421832788</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>20691.1301419956</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>22131.4326853904</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>22453.2541080813</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>24933.5303929859</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>26409.8249414399</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>27824.3529280982</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>0.026</t>
+          <t>29902.516880429</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32774.0077219302</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>33829.1280062003</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34681.9341234074</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35499.9376077861</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35228.0573745961</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>34692.4789337632</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32049.234143152</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>31370.9157231393</t>
         </is>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>32840.9826920421</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>35872.5350230286</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>38093.8174407546</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41046.0187968421</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>42748.5301890244</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>43903.8085200079</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>41425.3334343181</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1859,144 +1864,144 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>118359.080492235</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>0.118</t>
+          <t>134155.221226511</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>142311.832033237</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>0.135</t>
+          <t>152588.503095332</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>154053.053593446</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.158</t>
+          <t>178691.762125545</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>204229.495604721</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>232925.144127347</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>238663.451121867</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>266127.19588495</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>310661.340638017</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>360563.353271981</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>401961.500427633</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>0.409</t>
+          <t>463922.475729894</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>0.352</t>
+          <t>399632.636798417</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>444490.09143236</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>470307.038360147</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>466629.282519669</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>454444.37211967</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>457191.417915088</t>
         </is>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>491880.488897662</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>506574.300700546</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>552654.478038459</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>600873.422730636</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.561</t>
+          <t>635875.767550112</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>652068.923781696</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>0.594</t>
+          <t>673757.840640793</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2006,144 +2011,144 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.301</t>
+          <t>3706966.84317901</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>3.287</t>
+          <t>3691369.8373418</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3.338</t>
+          <t>3748250.1503154</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>3.42</t>
+          <t>3840055.64308945</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>3.57</t>
+          <t>4008839.53682948</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>3.833</t>
+          <t>4304653.04305724</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>3.981</t>
+          <t>4470057.99132923</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>3.889</t>
+          <t>4367244.13224243</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>3.922</t>
+          <t>4404769.55907047</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>4.043</t>
+          <t>4540613.58345138</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>4.158</t>
+          <t>4669270.33109241</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>4.475</t>
+          <t>5025308.54639937</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>4.726</t>
+          <t>5307285.20857653</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>4.828</t>
+          <t>5421614.68131965</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>4.454</t>
+          <t>5000589.74657249</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>4.753</t>
+          <t>5337651.47911143</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>5.029</t>
+          <t>5647987.95899533</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>5.206</t>
+          <t>5847070.62080884</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>5.273</t>
+          <t>5921321.47839682</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>5.517</t>
+          <t>6195666.29667263</t>
         </is>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>5.638</t>
+          <t>6330945.79919102</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>5.829</t>
+          <t>6546065.15447875</t>
         </is>
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>6.211</t>
+          <t>6974054.84060711</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.234</t>
+          <t>7000402.7445219</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>6.411</t>
+          <t>7198921.7232676</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>6.636</t>
+          <t>7451421.682381</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>6.703</t>
+          <t>7526818.33439377</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2153,144 +2158,144 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>263288.91572914</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.245</t>
+          <t>274819.785106647</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>285859.10654421</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>293860.461816684</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.274</t>
+          <t>306749.317590544</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>343050.257643977</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>356873.443824914</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>368665.044278374</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>368662.828535107</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0.345</t>
+          <t>386221.2128344</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>418385.127158003</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>0.403</t>
+          <t>452176.133153141</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>0.423</t>
+          <t>474422.269767102</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>0.439</t>
+          <t>492476.042175243</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>0.394</t>
+          <t>441324.362877105</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>0.428</t>
+          <t>479976.621642326</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>0.437</t>
+          <t>490080.267783903</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>0.455</t>
+          <t>510479.579959017</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>0.456</t>
+          <t>510794.327958972</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>538283.593744348</t>
         </is>
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.493</t>
+          <t>552930.754579209</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>0.512</t>
+          <t>573706.492309115</t>
         </is>
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>593533.23020223</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>0.547</t>
+          <t>612891.858543039</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>642762.389516385</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>624360.805005696</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>0.568</t>
+          <t>636272.368509847</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2300,144 +2305,144 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>0.806</t>
+          <t>859503.380100947</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.889</t>
+          <t>947116.541728794</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.922</t>
+          <t>982434.809862531</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>1051129.48989046</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>1.077</t>
+          <t>1147938.92242739</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1311295.89869531</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.343</t>
+          <t>1431634.69507259</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.445</t>
+          <t>1539707.90321317</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>1.555</t>
+          <t>1657721.58924507</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>1.682</t>
+          <t>1792743.78287627</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>1.858</t>
+          <t>1980504.22952974</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2.052</t>
+          <t>2187462.84938103</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2.166</t>
+          <t>2308486.54247903</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>2.157</t>
+          <t>2298966.76437042</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2099586.02604678</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1.985</t>
+          <t>2116019.76702789</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>2103230.64554607</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1.924</t>
+          <t>2051045.42096355</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>1.899</t>
+          <t>2023845.42637262</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
         <is>
-          <t>1.927</t>
+          <t>2053554.69510555</t>
         </is>
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>2.025</t>
+          <t>2157887.80565579</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>2.086</t>
+          <t>2223132.542064</t>
         </is>
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2.164</t>
+          <t>2306474.18861627</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>2.275</t>
+          <t>2424251.67725151</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.319</t>
+          <t>2471195.08591979</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2.401</t>
+          <t>2559136.06302147</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2555524.82365583</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2447,144 +2452,144 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8043.87289613303</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>8760.2753962796</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>10782.2072462326</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>11967.6807728505</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>12451.8099100244</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>14630.3631015085</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>15926.5167391027</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>17806.899023183</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>19068.3786727012</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>21204.0984891961</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>24499.9104493946</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>29342.2062660499</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>34814.6980647248</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>35232.1202879327</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>28737.8087240939</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>32024.2771132468</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>38238.3094371377</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>0.039</t>
+          <t>41378.8588872986</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>43185.3420465759</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>43605.9236174888</t>
         </is>
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>44478.8273408168</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>46701.7368743369</t>
         </is>
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>50108.7747737238</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>0.051</t>
+          <t>54970.8271496297</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>59701.742776127</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>60780.227422708</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>63209.4217592055</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2594,144 +2599,144 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>175721.949624342</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>0.191</t>
+          <t>176544.821713752</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>189500.043268624</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>0.218</t>
+          <t>201525.100363404</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>212852.320813665</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>245390.499488876</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>0.273</t>
+          <t>252757.526235691</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>257795.353220195</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>263294.071644775</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0.301</t>
+          <t>278559.822149439</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>0.323</t>
+          <t>298356.208855611</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>318184.936632884</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>345299.441973469</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>0.389</t>
+          <t>359199.061783256</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>322977.511116371</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>340034.42149458</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>360743.953168495</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>0.397</t>
+          <t>367240.543381338</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>368104.275973607</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>375320.550498785</t>
         </is>
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>0.415</t>
+          <t>383632.056078521</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>0.426</t>
+          <t>394325.101803166</t>
         </is>
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>0.447</t>
+          <t>413657.093340666</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>0.464</t>
+          <t>429165.069070396</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>442990.262661281</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>453304.971990409</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>453367.621417586</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2741,144 +2746,144 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2.106</t>
+          <t>1942369.98729448</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.199</t>
+          <t>2028936.87741258</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2.23</t>
+          <t>2057549.98603441</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.374</t>
+          <t>2190284.04861109</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>2.505</t>
+          <t>2310533.01769814</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2.713</t>
+          <t>2503705.99087466</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>2.842</t>
+          <t>2621936.43407908</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.934</t>
+          <t>2707518.70878533</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>2.967</t>
+          <t>2737255.1959641</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>2882816.92400237</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>3.241</t>
+          <t>2990534.64041487</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>3.459</t>
+          <t>3191111.84973196</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>3.629</t>
+          <t>3348644.92372462</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>3.676</t>
+          <t>3392017.29957864</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>3196444.75686196</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>3.621</t>
+          <t>3340894.0440918</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>3.778</t>
+          <t>3485457.34983882</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>3.888</t>
+          <t>3587051.80146028</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>3.867</t>
+          <t>3566631.58253858</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
         <is>
-          <t>3.967</t>
+          <t>3659190.62056528</t>
         </is>
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.068</t>
+          <t>3752808.49205367</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>4.066</t>
+          <t>3750314.86070432</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>4.178</t>
+          <t>3854141.09976864</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>4.361</t>
+          <t>4023259.46447172</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>4.484</t>
+          <t>4136763.69444211</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>4.464</t>
+          <t>4117289.35855292</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>4.527</t>
+          <t>4175986.24796728</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2888,144 +2893,144 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>2336726.93700647</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.914</t>
+          <t>2541754.62214784</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2.356</t>
+          <t>3128455.3268015</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>3358749.50820294</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>2.707</t>
+          <t>3594104.42255234</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>3.115</t>
+          <t>4136231.96335184</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>3.197</t>
+          <t>4244960.52320715</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>4354969.70035026</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>3.169</t>
+          <t>4207035.28053769</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>3.378</t>
+          <t>4483932.61328351</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>3.533</t>
+          <t>4689807.02771247</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>3.774</t>
+          <t>5009592.37599267</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>3.966</t>
+          <t>5265033.89995199</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>3.523</t>
+          <t>4677685.59888742</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>3.089</t>
+          <t>4101431.35083591</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>4487486.5713447</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>3.465</t>
+          <t>4600240.85949706</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>3.775</t>
+          <t>5013018.67513661</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>3.762</t>
+          <t>4994869.25201331</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
         <is>
-          <t>4.104</t>
+          <t>5449915.49955852</t>
         </is>
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>4.723</t>
+          <t>6271029.50573667</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>4.225</t>
+          <t>5609089.73128654</t>
         </is>
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>4.145</t>
+          <t>5502301.10050306</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>4.371</t>
+          <t>5804244.09140028</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>4.561</t>
+          <t>6055990.71042409</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>4.625</t>
+          <t>6141249.86940272</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>6200895.21132567</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3035,144 +3040,144 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>146919.000424263</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>160543.287720476</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>172506.789456123</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>179577.512478247</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>0.216</t>
+          <t>193165.109974941</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>203890.272149812</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>215888.326198619</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>226542.677932053</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>0.276</t>
+          <t>247227.599613398</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0.294</t>
+          <t>263131.806550565</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>0.303</t>
+          <t>271211.290813374</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>301320.878099086</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>320064.468149531</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>330023.857800945</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>0.35</t>
+          <t>313696.718657107</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>0.363</t>
+          <t>325549.225621772</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>0.329</t>
+          <t>294542.85235708</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>291009.076511744</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>0.309</t>
+          <t>276365.188732283</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>265928.213683709</t>
         </is>
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.295</t>
+          <t>264279.911108152</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>0.291</t>
+          <t>260619.745566363</t>
         </is>
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>0.304</t>
+          <t>272274.265324191</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>0.311</t>
+          <t>278210.84009187</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>285107.904192593</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>0.324</t>
+          <t>289870.149839984</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>301964.752772851</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3182,144 +3187,144 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>60279.4896582501</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>63151.9650009584</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>73652.8036842719</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>79481.4392778964</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>86884.8825566775</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>0.108</t>
+          <t>102052.036170477</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.125</t>
+          <t>118350.617722364</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>137983.578769567</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.151</t>
+          <t>143072.824477764</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0.17</t>
+          <t>160650.240422115</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>0.187</t>
+          <t>176955.161166558</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>0.199</t>
+          <t>188294.58655651</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>209233.074775272</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>220835.149551272</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>181414.758953145</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>197528.222208231</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>207173.07245317</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>0.207</t>
+          <t>196062.737185524</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>197751.019641684</t>
         </is>
       </c>
       <c r="V24" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>207227.013826615</t>
         </is>
       </c>
       <c r="W24" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>222630.150519242</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>0.242</t>
+          <t>228396.590963669</t>
         </is>
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>245586.551198356</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>269669.07273587</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>0.299</t>
+          <t>282356.475586006</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>0.312</t>
+          <t>295207.486975839</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>0.321</t>
+          <t>303566.389428141</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3329,144 +3334,144 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.487</t>
+          <t>646782.677082662</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.538</t>
+          <t>714849.079738505</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.665</t>
+          <t>883834.867966698</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.668</t>
+          <t>887407.530343927</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.761</t>
+          <t>1011459.62226251</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.926</t>
+          <t>1229542.67998627</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>1301096.04390797</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.001</t>
+          <t>1329874.91854735</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.989</t>
+          <t>1313609.44647064</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>1462468.4118203</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1725530.31797891</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>1.505</t>
+          <t>1999727.19612898</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.733</t>
+          <t>2302165.75374839</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.778</t>
+          <t>2361244.85933732</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.935</t>
+          <t>2570567.97933004</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>2.607</t>
+          <t>3462575.38642759</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>2.875</t>
+          <t>3818308.4059168</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>3.067</t>
+          <t>4074001.44393014</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>2.879</t>
+          <t>3823915.25598933</t>
         </is>
       </c>
       <c r="V25" t="inlineStr">
         <is>
-          <t>3.054</t>
+          <t>4057183.23832861</t>
         </is>
       </c>
       <c r="W25" t="inlineStr">
         <is>
-          <t>3.764</t>
+          <t>5000494.2737369</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>4.02</t>
+          <t>5339290.98713046</t>
         </is>
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>4.522</t>
+          <t>6006493.69944028</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>4.572</t>
+          <t>6073012.39830422</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>6628073.55596922</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>5.322</t>
+          <t>7069329.8866738</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>5.747</t>
+          <t>7633356.45153151</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3476,144 +3481,144 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>397558.900243698</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>0.387</t>
+          <t>456996.158245053</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0.417</t>
+          <t>492929.595634275</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>212470.898176162</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>330807.010936607</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>0.349</t>
+          <t>412150.500834354</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>416508.736220913</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>481093.55034888</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>484834.675107943</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0.407</t>
+          <t>481252.711431132</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>522204.004200978</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>661104.447467581</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>0.598</t>
+          <t>706298.983302735</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>777632.075869479</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>0.745</t>
+          <t>880260.399535857</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1.013</t>
+          <t>1195930.61259469</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1.155</t>
+          <t>1364457.34216535</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>1.299</t>
+          <t>1534107.92233827</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
         <is>
-          <t>1.248</t>
+          <t>1474243.92213543</t>
         </is>
       </c>
       <c r="V26" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1443050.53198691</t>
         </is>
       </c>
       <c r="W26" t="inlineStr">
         <is>
-          <t>1.383</t>
+          <t>1633430.96177407</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>1.486</t>
+          <t>1755271.38391843</t>
         </is>
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>1.568</t>
+          <t>1852281.93456657</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>1.554</t>
+          <t>1834765.16996602</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>1.737</t>
+          <t>2050884.22225146</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>1.829</t>
+          <t>2159704.06976427</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>1.949</t>
+          <t>2301750.97193893</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3623,144 +3628,144 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>113201.236398127</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>0.115</t>
+          <t>124899.19003776</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.144</t>
+          <t>155972.999063728</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>0.164</t>
+          <t>177343.415722674</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>0.19</t>
+          <t>206448.424850785</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>0.23</t>
+          <t>249382.509911672</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>285418.331351172</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>302846.657371232</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>0.298</t>
+          <t>325216.500143744</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>348402.052304229</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>0.351</t>
+          <t>384739.164044152</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>433270.132173107</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>0.42</t>
+          <t>460739.31013415</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>0.424</t>
+          <t>466026.586009802</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>406463.556865125</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>0.368</t>
+          <t>403663.296410514</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>394136.471643472</t>
         </is>
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>421338.553094245</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>440380.873585847</t>
         </is>
       </c>
       <c r="V27" t="inlineStr">
         <is>
-          <t>0.431</t>
+          <t>471113.827716497</t>
         </is>
       </c>
       <c r="W27" t="inlineStr">
         <is>
-          <t>0.596</t>
+          <t>644127.424012598</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>0.642</t>
+          <t>695019.948547931</t>
         </is>
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>740500.192356069</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>0.744</t>
+          <t>804243.489076136</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>925141.051042164</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>0.906</t>
+          <t>982626.573284536</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>0.927</t>
+          <t>1006039.8106133</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3770,144 +3775,144 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1.687</t>
+          <t>1908019.38370154</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>1.928</t>
+          <t>2181204.61964086</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>2.045</t>
+          <t>2313739.36358511</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2.102</t>
+          <t>2378156.6326988</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>2.225</t>
+          <t>2517103.46546794</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2.448</t>
+          <t>2769423.7677936</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>2.578</t>
+          <t>2915993.9723354</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>3006233.24386309</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>2.738</t>
+          <t>3097301.23801257</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>3212910.07063285</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>2.958</t>
+          <t>3345839.78621777</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>3.125</t>
+          <t>3534811.12401302</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>3.251</t>
+          <t>3677352.66619573</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>3.322</t>
+          <t>3757313.16438583</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>3416077.06608966</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>3.204</t>
+          <t>3624624.2020844</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>3.292</t>
+          <t>3723779.81715512</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>3.225</t>
+          <t>3648372.1811873</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3597517.30071774</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>3.193</t>
+          <t>3612458.54405885</t>
         </is>
       </c>
       <c r="W28" t="inlineStr">
         <is>
-          <t>3.258</t>
+          <t>3686005.18901625</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>3.357</t>
+          <t>3797761.42460763</t>
         </is>
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>3.454</t>
+          <t>3906905.940263</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>3.562</t>
+          <t>4029556.16245542</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>3.581</t>
+          <t>4050777.60813472</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>3.621</t>
+          <t>4096412.82742989</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>3.645</t>
+          <t>4122972.1401125</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3917,144 +3922,144 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>7.638</t>
+          <t>10627182.4204631</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.052</t>
+          <t>9812102.18058482</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>7.358</t>
+          <t>10238281.1927173</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>6.674</t>
+          <t>9286239.61959106</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>7.967</t>
+          <t>11086378.4830545</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>9.985</t>
+          <t>13893825.9682117</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>8.966</t>
+          <t>12476560.984242</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>8.15</t>
+          <t>11340252.2669083</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>7.312</t>
+          <t>10175083.3143556</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>7.257</t>
+          <t>10099082.6429564</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>7.333</t>
+          <t>10204569.6996867</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>6.935</t>
+          <t>9650004.22497911</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>6.511</t>
+          <t>9060080.29203513</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>6.951</t>
+          <t>9672906.78959293</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>7.221</t>
+          <t>10048940.1343891</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>8.171</t>
+          <t>11371111.3892627</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>8.727</t>
+          <t>12143830.4858726</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>9.207</t>
+          <t>12811809.9570958</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>7.432</t>
+          <t>10342082.7130001</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
-          <t>7.174</t>
+          <t>9983369.70646028</t>
         </is>
       </c>
       <c r="W29" t="inlineStr">
         <is>
-          <t>7.719</t>
+          <t>10741728.7629672</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>8.673</t>
+          <t>12069148.8009229</t>
         </is>
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>8.305</t>
+          <t>11556869.8158417</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>8.267</t>
+          <t>11504015.544107</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>8.896</t>
+          <t>12378955.1481231</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>8.953</t>
+          <t>12458057.3528912</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>9.023</t>
+          <t>12555468.6038892</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -4064,144 +4069,144 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>0.869</t>
+          <t>1134965.43546709</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>0.975</t>
+          <t>1273905.00913908</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>1331859.03003765</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>927002.064653267</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>0.973</t>
+          <t>1269641.1815062</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>1758611.33877191</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1.282</t>
+          <t>1674402.65153181</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1.386</t>
+          <t>1810339.60879575</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>1.306</t>
+          <t>1706994.76438443</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>1855304.39152482</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>1.707</t>
+          <t>2229770.93222595</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>1.934</t>
+          <t>2525543.36900993</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2.013</t>
+          <t>2628948.47986759</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>2336095.86555555</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>1.621</t>
+          <t>2117523.74710528</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>2818254.91569721</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>2.323</t>
+          <t>3030940.89959078</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>2.543</t>
+          <t>3318473.09761543</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>2.535</t>
+          <t>3309690.6625741</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
-          <t>2.961</t>
+          <t>3872393.27904267</t>
         </is>
       </c>
       <c r="W30" t="inlineStr">
         <is>
-          <t>3.536</t>
+          <t>4626216.57446518</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>3.553</t>
+          <t>4648763.71421275</t>
         </is>
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>3.795</t>
+          <t>4963824.13734091</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>3.861</t>
+          <t>5050895.90338274</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>3.847</t>
+          <t>5034999.51958596</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>3.925</t>
+          <t>5137553.31786546</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>4.151</t>
+          <t>5432938.49575895</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -4211,144 +4216,144 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11266.3216425826</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14227.196952276</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>19372.4484295735</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>21545.0945838597</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>21394.0578968097</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>0.021</t>
+          <t>26086.0493649402</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.024</t>
+          <t>28846.591918961</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>0.027</t>
+          <t>32766.563999545</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>34505.4231858228</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>37991.8529595516</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>44896.8666306538</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>51687.0940388879</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>60753.0814103217</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>70543.6422327505</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>55940.0870705774</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>59421.1729714737</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>68987.5467725817</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>72961.5155845789</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>74790.7649752724</t>
         </is>
       </c>
       <c r="V31" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>76947.2815753448</t>
         </is>
       </c>
       <c r="W31" t="inlineStr">
         <is>
-          <t>0.064</t>
+          <t>78445.572373855</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>81612.237567575</t>
         </is>
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>0.074</t>
+          <t>90343.0603350119</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>97255.8062508425</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>102770.930184601</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>105629.092683039</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>106727.50150344</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -4358,144 +4363,144 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>0.029</t>
+          <t>36665.8352145377</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>39795.1864251302</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>42270.1756421258</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>46378.3697045147</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>55868.5933498895</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>67673.7844039663</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>70324.1500000365</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>71416.3385521332</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>0.059</t>
+          <t>73513.0528413193</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0.067</t>
+          <t>83072.6597441611</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>92870.4307264679</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>110106.080094352</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>123119.2579273</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>0.102</t>
+          <t>127422.024626144</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>114464.033980091</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>0.107</t>
+          <t>132998.053239989</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>122579.004609625</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>0.121</t>
+          <t>150414.910317923</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>163951.909265426</t>
         </is>
       </c>
       <c r="V32" t="inlineStr">
         <is>
-          <t>0.156</t>
+          <t>193611.481422264</t>
         </is>
       </c>
       <c r="W32" t="inlineStr">
         <is>
-          <t>0.168</t>
+          <t>209303.006692797</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>220233.630640894</t>
         </is>
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>0.186</t>
+          <t>231173.429174819</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>239869.715182347</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>254279.197215001</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>267450.058805664</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>276644.440872672</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -4505,144 +4510,144 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>10092.7760760491</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11576.3214940614</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>14162.1836367563</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>15532.8452355142</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17038.0415870432</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>0.017</t>
+          <t>20715.6937793896</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.018</t>
+          <t>22021.0448035914</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23908.5059002517</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>24731.2298382373</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>29185.2449255487</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>34601.9322028702</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>43211.9555584388</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>56394.2909307087</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>60829.757645841</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>47785.4170412707</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>46527.4557360349</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>50789.8610878964</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>55556.1823665037</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>57145.8323451853</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
-          <t>0.046</t>
+          <t>57130.9869802335</t>
         </is>
       </c>
       <c r="W33" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>60807.2053418092</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>0.049</t>
+          <t>61175.4074086199</t>
         </is>
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>67348.8416131024</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>0.058</t>
+          <t>72358.5169559256</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>74553.628149456</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>76964.6811569552</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>78835.3425184152</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -4652,144 +4657,144 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.475</t>
+          <t>631556.251565466</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.563</t>
+          <t>748400.396024058</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>1022530.06486028</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.832</t>
+          <t>1104867.60998382</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.984</t>
+          <t>1307039.18265217</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>1.334</t>
+          <t>1772074.64830654</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>1.437</t>
+          <t>1909111.93654025</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>1.367</t>
+          <t>1816071.06887321</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1403509.60312537</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>1.031</t>
+          <t>1369580.80420273</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>1.155</t>
+          <t>1534965.2165058</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.288</t>
+          <t>1711376.64621006</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.267</t>
+          <t>1682909.65764369</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.266</t>
+          <t>1682421.84481655</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.061</t>
+          <t>1409337.77529932</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1751039.88102694</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1.414</t>
+          <t>1878499.69185969</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>1.597</t>
+          <t>2121474.1962553</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>2140437.74611104</t>
         </is>
       </c>
       <c r="V34" t="inlineStr">
         <is>
-          <t>1.681</t>
+          <t>2232986.74090023</t>
         </is>
       </c>
       <c r="W34" t="inlineStr">
         <is>
-          <t>1.759</t>
+          <t>2336719.50948354</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>1.629</t>
+          <t>2163846.77412707</t>
         </is>
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>2337500.7478722</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>1.791</t>
+          <t>2379799.41336283</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>1.933</t>
+          <t>2568642.36090278</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>1.978</t>
+          <t>2627896.38704321</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>2.022</t>
+          <t>2685606.21173541</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4799,144 +4804,144 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7305.23849930163</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>0.006</t>
+          <t>7927.83544558214</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>8503.60072364967</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>0.007</t>
+          <t>9005.30540205479</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>0.008</t>
+          <t>9920.83764932827</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11656.1785183625</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11662.5023979265</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11310.0784042613</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11587.8005742193</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0.009</t>
+          <t>11363.2088777854</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>12675.3784349407</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>0.011</t>
+          <t>13549.5001613168</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14673.6301054626</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>0.012</t>
+          <t>14888.9678113117</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>0.013</t>
+          <t>16026.3517328932</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>17400.8265194214</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>0.014</t>
+          <t>16835.0166130179</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>0.015</t>
+          <t>18534.7175006438</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
         <is>
-          <t>0.016</t>
+          <t>19617.4576543388</t>
         </is>
       </c>
       <c r="V35" t="inlineStr">
         <is>
-          <t>0.019</t>
+          <t>23699.5852821213</t>
         </is>
       </c>
       <c r="W35" t="inlineStr">
         <is>
-          <t>0.022</t>
+          <t>27366.7472542499</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>0.023</t>
+          <t>28107.2609905556</t>
         </is>
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>0.025</t>
+          <t>31155.6962097195</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>0.028</t>
+          <t>35075.4876269131</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>37340.3460821956</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>38972.5378906953</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>37734.8104568555</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4946,144 +4951,144 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>0.597</t>
+          <t>749947.611761595</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>0.626</t>
+          <t>785684.466330377</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>804358.825746743</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>0.683</t>
+          <t>857787.526922394</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>0.733</t>
+          <t>920184.961144476</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>0.811</t>
+          <t>1017994.00564085</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.888</t>
+          <t>1115261.28866616</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.902</t>
+          <t>1132398.75002899</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>0.912</t>
+          <t>1144909.98197689</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>1189886.0187205</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>0.988</t>
+          <t>1241101.2444414</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>1.045</t>
+          <t>1312563.07923827</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>1.096</t>
+          <t>1376753.54954657</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>1.139</t>
+          <t>1429830.80800834</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>1.117</t>
+          <t>1403084.70368719</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1.144</t>
+          <t>1436444.46962333</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1.182</t>
+          <t>1484622.55069828</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>1.222</t>
+          <t>1534623.14846375</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
         <is>
-          <t>1.226</t>
+          <t>1539180.59693338</t>
         </is>
       </c>
       <c r="V36" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1570167.04489561</t>
         </is>
       </c>
       <c r="W36" t="inlineStr">
         <is>
-          <t>1.291</t>
+          <t>1620795.75100398</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1657967.11915063</t>
         </is>
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1745112.99805513</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>1.448</t>
+          <t>1817985.64728884</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>1.498</t>
+          <t>1881434.68010544</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>1.532</t>
+          <t>1923517.18188441</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1996223.26574027</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5093,144 +5098,144 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>263883.648437202</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>301966.83163846</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>336678.358411154</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>0.289</t>
+          <t>372547.019343711</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>382138.632520686</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>455903.552703838</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>523860.966222264</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.402</t>
+          <t>518602.67654356</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>0.373</t>
+          <t>481124.890241945</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>513907.040150566</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>617213.044302263</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>710828.094301578</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>0.636</t>
+          <t>819081.502562303</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>0.738</t>
+          <t>950436.465124634</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>776904.64154423</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>915734.418810048</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>0.754</t>
+          <t>971658.532718555</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>0.769</t>
+          <t>991521.163760537</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
         <is>
-          <t>0.774</t>
+          <t>997574.736511539</t>
         </is>
       </c>
       <c r="V37" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>1031592.33182184</t>
         </is>
       </c>
       <c r="W37" t="inlineStr">
         <is>
-          <t>0.848</t>
+          <t>1091845.31147809</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>1088841.67054965</t>
         </is>
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>0.919</t>
+          <t>1183524.38473094</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>0.986</t>
+          <t>1270886.50438977</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>1.055</t>
+          <t>1360565.19179499</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>1.099</t>
+          <t>1417436.25962034</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>1.116</t>
+          <t>1438564.24017073</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5240,144 +5245,144 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>0.166</t>
+          <t>227959.93585918</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>246968.85061581</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>0.193</t>
+          <t>264879.105265816</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>0.206</t>
+          <t>281723.832283131</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>0.222</t>
+          <t>304203.724930674</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>0.246</t>
+          <t>337644.656445048</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>0.258</t>
+          <t>353822.78587401</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>0.265</t>
+          <t>363587.571886971</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>0.269</t>
+          <t>368035.982380887</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>390323.017592486</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>405324.044752263</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>0.313</t>
+          <t>429033.477275703</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>0.325</t>
+          <t>445648.620154888</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>0.339</t>
+          <t>464287.53150997</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>0.318</t>
+          <t>436479.012938816</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>454261.76852432</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>0.331</t>
+          <t>453670.605407486</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>0.314</t>
+          <t>429664.078431968</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>431579.818355482</t>
         </is>
       </c>
       <c r="V38" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>439210.513497118</t>
         </is>
       </c>
       <c r="W38" t="inlineStr">
         <is>
-          <t>0.333</t>
+          <t>455745.337245873</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>0.342</t>
+          <t>469313.29664355</t>
         </is>
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>0.362</t>
+          <t>496395.565362109</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>0.385</t>
+          <t>527138.318274491</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>0.395</t>
+          <t>541945.660163874</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>553735.515857442</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>0.404</t>
+          <t>553632.313063426</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5387,144 +5392,144 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>76395.7014494139</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>81260.7787728893</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>0.062</t>
+          <t>87443.9697625209</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>97449.3690261279</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>0.063</t>
+          <t>89757.6079678161</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>112778.49727224</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>120656.73424283</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>130950.971640606</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>0.099</t>
+          <t>140502.773009196</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0.116</t>
+          <t>165330.827727063</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0.146</t>
+          <t>208075.877375472</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>255844.832202755</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>0.234</t>
+          <t>334057.867343559</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>0.259</t>
+          <t>369310.984939556</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>0.235</t>
+          <t>335710.712285643</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>0.229</t>
+          <t>326633.264346995</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>341319.114225325</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>343143.551513439</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
         <is>
-          <t>0.255</t>
+          <t>364173.408794827</t>
         </is>
       </c>
       <c r="V39" t="inlineStr">
         <is>
-          <t>0.263</t>
+          <t>375775.650102517</t>
         </is>
       </c>
       <c r="W39" t="inlineStr">
         <is>
-          <t>0.285</t>
+          <t>407678.444781223</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>0.297</t>
+          <t>425600.907412109</t>
         </is>
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>0.326</t>
+          <t>465878.807689049</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>0.356</t>
+          <t>510228.491350337</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>0.396</t>
+          <t>567396.239923035</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>562115.452574153</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>0.399</t>
+          <t>572045.89346898</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -5534,144 +5539,144 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>0.582</t>
+          <t>670398.361125671</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>671723.582196104</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>752926.355621792</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>0.445</t>
+          <t>514462.415146878</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>0.344</t>
+          <t>399854.676811498</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>595717.91525172</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.648</t>
+          <t>750674.130685232</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.677</t>
+          <t>782871.039381222</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>0.698</t>
+          <t>807104.095999502</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0.831</t>
+          <t>962940.365959055</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>1.056</t>
+          <t>1222135.7512964</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>1.353</t>
+          <t>1563639.72829133</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>1.669</t>
+          <t>1925139.94910544</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>1.943</t>
+          <t>2243222.51701126</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>1.524</t>
+          <t>1760160.00211961</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>2.036</t>
+          <t>2346944.56341929</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>2.469</t>
+          <t>2846383.91183475</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>2.957</t>
+          <t>3401405.95236824</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
         <is>
-          <t>2.94</t>
+          <t>3375975.11967139</t>
         </is>
       </c>
       <c r="V40" t="inlineStr">
         <is>
-          <t>2.602</t>
+          <t>2987528.65616858</t>
         </is>
       </c>
       <c r="W40" t="inlineStr">
         <is>
-          <t>2.139</t>
+          <t>2458986.13013098</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>1.965</t>
+          <t>2255760.37371771</t>
         </is>
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2.418</t>
+          <t>2776697.60365345</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>2.398</t>
+          <t>2761816.99118426</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2.619</t>
+          <t>3012192.49075943</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2.673</t>
+          <t>3074789.80186403</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>2.694</t>
+          <t>3104956.00354163</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5681,144 +5686,144 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>43114.3391896904</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>0.034</t>
+          <t>48041.1787225426</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.041</t>
+          <t>56925.6003602804</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>58868.1344733404</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>55241.0882717346</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>66811.4476228073</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.052</t>
+          <t>72685.9916257916</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.057</t>
+          <t>79646.6314364474</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>0.065</t>
+          <t>90479.6642357113</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>102343.079778927</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>118808.628422212</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>0.104</t>
+          <t>144496.486334708</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>0.126</t>
+          <t>176070.580120211</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>204786.36094557</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>0.136</t>
+          <t>189127.132995572</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>0.149</t>
+          <t>207890.572511841</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>222661.212959426</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>235320.222644822</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
         <is>
-          <t>0.169</t>
+          <t>236371.601240104</t>
         </is>
       </c>
       <c r="V41" t="inlineStr">
         <is>
-          <t>0.173</t>
+          <t>240697.962959426</t>
         </is>
       </c>
       <c r="W41" t="inlineStr">
         <is>
-          <t>0.182</t>
+          <t>254380.843208968</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>0.181</t>
+          <t>253155.034249271</t>
         </is>
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>0.192</t>
+          <t>268040.625196381</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>0.204</t>
+          <t>284680.477583729</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>0.209</t>
+          <t>291009.633855873</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>307532.768574081</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>310797.83436011</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5828,144 +5833,144 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>0.031</t>
+          <t>43409.5182216802</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>0.032</t>
+          <t>45490.9502312238</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.035</t>
+          <t>49555.6591750823</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>53027.4736195216</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>56349.4629836537</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>58999.4606835631</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.044</t>
+          <t>62618.4265991279</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.047</t>
+          <t>66487.110253563</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>70047.3846787467</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0.053</t>
+          <t>74083.5086087158</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>0.056</t>
+          <t>79423.0891551823</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>86426.2615947887</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>98887.9440806878</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>0.075</t>
+          <t>105386.498827615</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>0.069</t>
+          <t>96582.5803046021</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>0.07</t>
+          <t>98683.4628215453</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>103367.311644521</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>101020.506110679</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>101130.194071432</t>
         </is>
       </c>
       <c r="V42" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>102335.974460575</t>
         </is>
       </c>
       <c r="W42" t="inlineStr">
         <is>
-          <t>0.076</t>
+          <t>107159.87672243</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>0.079</t>
+          <t>111364.12598335</t>
         </is>
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>0.085</t>
+          <t>120236.334284877</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>0.091</t>
+          <t>128186.869836628</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>135916.527471233</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>142880.163957492</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>0.101</t>
+          <t>142183.724434606</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5975,144 +5980,144 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>0.364</t>
+          <t>535909.251903209</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>0.411</t>
+          <t>603993.323603591</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0.429</t>
+          <t>631112.643250877</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>0.442</t>
+          <t>649995.301396762</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>0.468</t>
+          <t>688574.210477393</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>0.528</t>
+          <t>776128.547568127</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.506</t>
+          <t>744146.854235163</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.529</t>
+          <t>778011.145170323</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>0.546</t>
+          <t>802457.321187352</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0.569</t>
+          <t>836168.365335492</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>0.595</t>
+          <t>875789.122998184</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>940971.269736614</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>0.684</t>
+          <t>1006290.45279449</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>0.662</t>
+          <t>973244.129157025</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>0.573</t>
+          <t>842237.920701493</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>0.689</t>
+          <t>1013810.42013432</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>0.756</t>
+          <t>1112597.34612111</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>0.798</t>
+          <t>1173029.4895619</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
         <is>
-          <t>0.805</t>
+          <t>1183616.80605351</t>
         </is>
       </c>
       <c r="V43" t="inlineStr">
         <is>
-          <t>0.789</t>
+          <t>1159791.36393044</t>
         </is>
       </c>
       <c r="W43" t="inlineStr">
         <is>
-          <t>0.818</t>
+          <t>1202634.26524415</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>0.829</t>
+          <t>1219231.12052387</t>
         </is>
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>0.857</t>
+          <t>1261166.17844233</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>0.859</t>
+          <t>1263981.21570293</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>0.866</t>
+          <t>1273161.24010873</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>0.871</t>
+          <t>1281280.6652979</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>1321169.80675111</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6122,144 +6127,144 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>0.282</t>
+          <t>312237.983091917</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>363262.059993164</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0.371</t>
+          <t>411322.15892173</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>0.392</t>
+          <t>434369.789683906</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>0.398</t>
+          <t>440842.6215799</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>0.519</t>
+          <t>574285.65014789</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.406</t>
+          <t>449566.81970937</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>522510.852948881</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>575846.87619086</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0.625</t>
+          <t>691648.757016702</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>0.777</t>
+          <t>860622.334568401</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>0.854</t>
+          <t>945580.34585604</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>0.976</t>
+          <t>1080683.82066387</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>1.022</t>
+          <t>1131846.88648862</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>0.839</t>
+          <t>929215.653803689</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1.069</t>
+          <t>1184403.83809137</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1.124</t>
+          <t>1245022.69166228</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>1.354</t>
+          <t>1500110.84892661</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
         <is>
-          <t>1.357</t>
+          <t>1503522.68673979</t>
         </is>
       </c>
       <c r="V44" t="inlineStr">
         <is>
-          <t>1.333</t>
+          <t>1476808.38849374</t>
         </is>
       </c>
       <c r="W44" t="inlineStr">
         <is>
-          <t>1.474</t>
+          <t>1632194.094883</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>1.483</t>
+          <t>1643294.03593103</t>
         </is>
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>1.443</t>
+          <t>1598012.82363281</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>1.277</t>
+          <t>1414732.49964263</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>1.279</t>
+          <t>1416694.41271111</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1505975.78754704</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>1.409</t>
+          <t>1561163.76940694</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6269,144 +6274,144 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>0.421</t>
+          <t>475263.542590576</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>0.435</t>
+          <t>491001.056995797</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>587091.90414845</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>547843.938566553</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>0.556</t>
+          <t>628608.206751655</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>0.725</t>
+          <t>819205.170695925</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.654</t>
+          <t>738777.813417273</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.641</t>
+          <t>723573.730454305</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>0.579</t>
+          <t>654348.199876359</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>697878.72323561</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>0.672</t>
+          <t>759637.08724241</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>0.712</t>
+          <t>804577.896172103</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>0.682</t>
+          <t>770957.050519986</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>0.687</t>
+          <t>775674.029371982</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>0.619</t>
+          <t>699219.279455981</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>0.808</t>
+          <t>912822.672753282</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>0.842</t>
+          <t>951359.974829111</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>0.931</t>
+          <t>1052126.69145145</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
         <is>
-          <t>0.934</t>
+          <t>1055389.74583558</t>
         </is>
       </c>
       <c r="V45" t="inlineStr">
         <is>
-          <t>0.987</t>
+          <t>1115539.11726456</t>
         </is>
       </c>
       <c r="W45" t="inlineStr">
         <is>
-          <t>1.149</t>
+          <t>1297715.01317107</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>1.172</t>
+          <t>1324491.74875614</t>
         </is>
       </c>
       <c r="Y45" t="inlineStr">
         <is>
-          <t>1.251</t>
+          <t>1413819.35475018</t>
         </is>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>1.232</t>
+          <t>1392125.47837996</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>1.303</t>
+          <t>1471999.60259108</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1502034.85560687</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>1.338</t>
+          <t>1511549.20031377</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6416,144 +6421,144 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>10.799</t>
+          <t>14316027.450007</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11.679</t>
+          <t>15482370.4659364</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>13.756</t>
+          <t>18236389.4587524</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>14.786</t>
+          <t>19602052.0724249</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>16.455</t>
+          <t>21813882.7112423</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>20.522</t>
+          <t>27206266.4156403</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>21.714</t>
+          <t>28786218.1183071</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>20.911</t>
+          <t>27721943.9536544</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>18.304</t>
+          <t>24265331.3004351</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>17.872</t>
+          <t>23692651.2799394</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>19.357</t>
+          <t>25661134.4669227</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>20.337</t>
+          <t>26960137.534798</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>19.517</t>
+          <t>25874311.9871135</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>18.796</t>
+          <t>24918365.6717005</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>18.269</t>
+          <t>24219324.5582273</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>20.397</t>
+          <t>27039994.168802</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>20.499</t>
+          <t>27176170.7102962</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>22.754</t>
+          <t>30165290.2912451</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>30477348.9151133</t>
         </is>
       </c>
       <c r="V46" t="inlineStr">
         <is>
-          <t>23.786</t>
+          <t>31533434.9816241</t>
         </is>
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>29.628</t>
+          <t>39277760.9895018</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>29.931</t>
+          <t>39679830.8574094</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>30.653</t>
+          <t>40636341.1374142</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>31.049</t>
+          <t>41161545.932684</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>34.291</t>
+          <t>45459001.3887039</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>34.858</t>
+          <t>46211163.9990955</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>35.101</t>
+          <t>46533314.3555426</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6565,7 +6570,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6575,144 +6580,144 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>43.349</t>
+          <t>54350274.2827501</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>45.677</t>
+          <t>57209883.8151937</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>51.181</t>
+          <t>64271647.1876827</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>51.473</t>
+          <t>64622574.1065296</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>56.414</t>
+          <t>71023838.1844459</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>68.559</t>
+          <t>86657240.0827002</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>70.325</t>
+          <t>88750773.4552537</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>68.945</t>
+          <t>86847033.7418469</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>64.708</t>
+          <t>81173223.2938115</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>66.874</t>
+          <t>83709594.9808901</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>73.555</t>
+          <t>92103355.3348949</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>79.902</t>
+          <t>99948801.7679264</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>83.248</t>
+          <t>103975761.651795</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>86.083</t>
+          <t>107515443.752738</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>83.853</t>
+          <t>105157924.510046</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>98.291</t>
+          <t>123532765.103892</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>105.781</t>
+          <t>133083978.216761</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>116.846</t>
+          <t>147268078.882938</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
         <is>
-          <t>116.108</t>
+          <t>146363425.745529</t>
         </is>
       </c>
       <c r="V48" t="inlineStr">
         <is>
-          <t>119.319</t>
+          <t>150601270.332599</t>
         </is>
       </c>
       <c r="W48" t="inlineStr">
         <is>
-          <t>135.06</t>
+          <t>171285779.629825</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>136.589</t>
+          <t>173305227.25441</t>
         </is>
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>142.874</t>
+          <t>181224134.969356</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>146.798</t>
+          <t>186509735.397727</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>157.028</t>
+          <t>199761577.622657</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>161.948</t>
+          <t>206167238.989671</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>166.699</t>
+          <t>212326779.862302</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6722,144 +6727,144 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>27796.6688905518</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>0.033</t>
+          <t>30411.6215540897</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>32955.6274767367</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>0.037</t>
+          <t>34576.4740725393</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>0.036</t>
+          <t>32954.6465364767</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>0.038</t>
+          <t>34893.5201123783</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>0.042</t>
+          <t>38590.6986002465</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>0.045</t>
+          <t>41919.3758104968</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>0.048</t>
+          <t>44675.1363082375</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0.054</t>
+          <t>49990.619048459</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>0.061</t>
+          <t>56509.215230515</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>0.066</t>
+          <t>61232.963378637</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67608.2351785124</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>73366.06319877</t>
         </is>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67762.6672202753</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67654.8084629261</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67607.8071154426</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>66938.3593954041</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
         <is>
-          <t>0.072</t>
+          <t>66096.0896974016</t>
         </is>
       </c>
       <c r="V49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67045.3629290227</t>
         </is>
       </c>
       <c r="W49" t="inlineStr">
         <is>
-          <t>0.073</t>
+          <t>67788.8167241964</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>0.078</t>
+          <t>71951.1921056565</t>
         </is>
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>0.082</t>
+          <t>75899.6707428583</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>0.087</t>
+          <t>80797.2550770953</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>0.089</t>
+          <t>82386.0000059252</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>0.092</t>
+          <t>85402.5979303745</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>0.097</t>
+          <t>89938.5145893579</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6869,144 +6874,144 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>0.494</t>
+          <t>546287.975952012</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>553541.852892575</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0.497</t>
+          <t>550686.948004601</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>0.518</t>
+          <t>572930.971199544</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>0.536</t>
+          <t>593734.428404173</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>645670.132164362</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>684272.970438466</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>0.634</t>
+          <t>702165.787526999</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>678465.972337924</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0.631</t>
+          <t>698749.564889556</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>0.663</t>
+          <t>734442.356782329</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>769061.577284861</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>0.703</t>
+          <t>778653.839042377</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>0.772</t>
+          <t>854329.310433851</t>
         </is>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>0.791</t>
+          <t>875592.198282184</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>0.908</t>
+          <t>1004799.81284272</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1.032</t>
+          <t>1142785.48383654</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>1187525.91593113</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
         <is>
-          <t>1.086</t>
+          <t>1202608.81832039</t>
         </is>
       </c>
       <c r="V50" t="inlineStr">
         <is>
-          <t>1.101</t>
+          <t>1219252.48233405</t>
         </is>
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>1.269</t>
+          <t>1405199.77454396</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1406287.00661254</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1398105.59403686</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>1.263</t>
+          <t>1398259.22479329</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>1.297</t>
+          <t>1436036.03167057</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>1.321</t>
+          <t>1461925.00732569</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>1512243.98098754</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -7016,144 +7021,144 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>0.201</t>
+          <t>232362.571663386</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>247639.371562509</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>0.241</t>
+          <t>278077.091061809</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>276541.325425346</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>0.262</t>
+          <t>303099.829185115</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>0.306</t>
+          <t>352757.928952879</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>0.332</t>
+          <t>382535.253755385</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>0.353</t>
+          <t>406712.020413292</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>0.348</t>
+          <t>401014.551955485</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0.361</t>
+          <t>416403.062595949</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>0.422</t>
+          <t>486177.903983024</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>0.472</t>
+          <t>543525.339049329</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>587680.449696803</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>0.552</t>
+          <t>635543.149603034</t>
         </is>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>0.485</t>
+          <t>559003.091237939</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>641483.732139764</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>0.605</t>
+          <t>697086.680225213</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>743262.939657614</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
         <is>
-          <t>0.643</t>
+          <t>742256.086210459</t>
         </is>
       </c>
       <c r="V51" t="inlineStr">
         <is>
-          <t>0.618</t>
+          <t>712758.41872121</t>
         </is>
       </c>
       <c r="W51" t="inlineStr">
         <is>
-          <t>0.583</t>
+          <t>673648.196354401</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>0.557</t>
+          <t>643232.850408519</t>
         </is>
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>0.592</t>
+          <t>683777.162308415</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>690245.233210688</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>0.602</t>
+          <t>695414.627876184</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>0.628</t>
+          <t>725178.903586739</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>0.638</t>
+          <t>736850.354685987</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -7163,144 +7168,144 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>0.223</t>
+          <t>255167.073421807</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>0.217</t>
+          <t>247480.879398336</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0.253</t>
+          <t>288767.90786975</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>265623.946377856</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>285461.310553646</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>338325.191840369</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>0.277</t>
+          <t>317136.786601553</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>297720.393704264</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0.337</t>
+          <t>384949.589290828</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0.401</t>
+          <t>457312.466617661</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>513167.616558645</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>539092.774852317</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>0.469</t>
+          <t>534889.220571794</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>0.434</t>
+          <t>494398.675146216</t>
         </is>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>0.467</t>
+          <t>532209.393377847</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>0.612</t>
+          <t>697241.617981521</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>0.651</t>
+          <t>741655.289446011</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>774457.124446553</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
         <is>
-          <t>0.599</t>
+          <t>682833.969811149</t>
         </is>
       </c>
       <c r="V52" t="inlineStr">
         <is>
-          <t>0.567</t>
+          <t>645860.730287133</t>
         </is>
       </c>
       <c r="W52" t="inlineStr">
         <is>
-          <t>0.627</t>
+          <t>713434.554274471</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>653778.197231217</t>
         </is>
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>0.666</t>
+          <t>758155.38577081</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>762689.738676672</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>0.681</t>
+          <t>774819.222662216</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>779969.829982085</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>797115.653464984</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -7310,144 +7315,144 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>1.326</t>
+          <t>1484455.69952338</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>1.449</t>
+          <t>1622329.01919549</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.611</t>
+          <t>1803970.60261967</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1.467</t>
+          <t>1642330.26155476</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>1.546</t>
+          <t>1730834.81763596</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>1.973</t>
+          <t>2209189.22032584</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>2.004</t>
+          <t>2243494.0470982</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>2193801.65194943</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>1.753</t>
+          <t>1962943.11159275</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>1.872</t>
+          <t>2096063.55581489</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2.171</t>
+          <t>2430878.31169162</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>2.447</t>
+          <t>2739785.17894606</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2.613</t>
+          <t>2925374.54388834</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>2.718</t>
+          <t>3043354.45788127</t>
         </is>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2.788</t>
+          <t>3120721.25122609</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>3.596</t>
+          <t>4025792.0579317</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>4.008</t>
+          <t>4486979.31594339</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>4.72</t>
+          <t>5284150.10327034</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>4.686</t>
+          <t>5245836.32417535</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
         <is>
-          <t>4.964</t>
+          <t>5556817.67024615</t>
         </is>
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>5.627</t>
+          <t>6299897.76900713</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>5.759</t>
+          <t>6447371.76440504</t>
         </is>
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>6.016</t>
+          <t>6735262.51919056</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>5.995</t>
+          <t>6711844.39168335</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>6.684</t>
+          <t>7482959.79087815</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>6.877</t>
+          <t>7698797.9716114</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>7.304</t>
+          <t>8176561.8559851</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -7457,144 +7462,144 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>1.158</t>
+          <t>1316886.09984971</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>1.195</t>
+          <t>1358327.59724716</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.494</t>
+          <t>1698870.0675151</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1.534</t>
+          <t>1744610.15482543</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>1.56</t>
+          <t>1774347.75289849</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>1.874</t>
+          <t>2130510.13005431</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1.944</t>
+          <t>2210534.6653118</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>1.499</t>
+          <t>1704019.81565892</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>1.318</t>
+          <t>1497777.54205334</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>1.406</t>
+          <t>1597956.74312613</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>1.673</t>
+          <t>1901492.74737248</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>1.925</t>
+          <t>2187211.03523995</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>2369959.07300123</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>2.326</t>
+          <t>2644158.49101929</t>
         </is>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2.349</t>
+          <t>2670539.05873407</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>2.899</t>
+          <t>3294527.49299801</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>3.076</t>
+          <t>3495627.31699808</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>3.665</t>
+          <t>4166569.49517246</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>3.675</t>
+          <t>4178034.51261552</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
         <is>
-          <t>3.692</t>
+          <t>4197378.09295626</t>
         </is>
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>4.342</t>
+          <t>4938674.79967723</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>4.062</t>
+          <t>4618938.85609387</t>
         </is>
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>4.319</t>
+          <t>4912335.81268077</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>3.989</t>
+          <t>4536172.42262659</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>3.968</t>
+          <t>4512592.81420635</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>3.984</t>
+          <t>4530757.10650853</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>4.038</t>
+          <t>4592320.20272923</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -7604,144 +7609,144 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>0.215</t>
+          <t>245921.134091221</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>0.214</t>
+          <t>243890.37287545</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>0.249</t>
+          <t>284967.500432286</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>0.228</t>
+          <t>260932.334636838</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>0.194</t>
+          <t>222023.675857919</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>0.219</t>
+          <t>249724.36213619</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>0.26</t>
+          <t>296800.995985054</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>0.279</t>
+          <t>318197.893535867</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0.286</t>
+          <t>326357.943638747</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0.336</t>
+          <t>384018.428536622</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>457140.906111636</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>0.474</t>
+          <t>541910.221677108</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>0.555</t>
+          <t>634064.740381153</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>731118.242250106</t>
         </is>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>0.495</t>
+          <t>565544.949221538</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>0.572</t>
+          <t>653241.272725927</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>0.635</t>
+          <t>725564.682266605</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>0.685</t>
+          <t>782782.040552982</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
         <is>
-          <t>0.709</t>
+          <t>809413.32470182</t>
         </is>
       </c>
       <c r="V55" t="inlineStr">
         <is>
-          <t>0.614</t>
+          <t>700765.943628349</t>
         </is>
       </c>
       <c r="W55" t="inlineStr">
         <is>
-          <t>0.574</t>
+          <t>655652.074183665</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>0.575</t>
+          <t>656917.048829123</t>
         </is>
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>0.644</t>
+          <t>735775.954134435</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>0.704</t>
+          <t>804085.506261315</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>902660.524372509</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>0.804</t>
+          <t>918389.738838523</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>0.845</t>
+          <t>965379.129212184</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -7751,144 +7756,144 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>0.505</t>
+          <t>592505.627363977</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>0.533</t>
+          <t>625822.770935417</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>719387.601502714</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>0.621</t>
+          <t>728294.771340205</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>772666.335974688</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>0.775</t>
+          <t>909433.050684548</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>0.824</t>
+          <t>966420.13571787</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>0.836</t>
+          <t>980886.234885506</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0.812</t>
+          <t>951509.547155193</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.881</t>
+          <t>1033662.98439914</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>1.041</t>
+          <t>1220153.80332753</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>1.254</t>
+          <t>1470057.4112649</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>1.345</t>
+          <t>1576461.08679319</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>1.548</t>
+          <t>1814264.24691506</t>
         </is>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>1.469</t>
+          <t>1723564.43503782</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1.823</t>
+          <t>2137998.84945831</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2275234.94969312</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>2.251</t>
+          <t>2639448.29866594</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>2.272</t>
+          <t>2665874.00674974</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
         <is>
-          <t>2.414</t>
+          <t>2833183.26128881</t>
         </is>
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>2.497</t>
+          <t>2931639.34390094</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>2.446</t>
+          <t>2872245.07720513</t>
         </is>
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2.459</t>
+          <t>2886518.29150743</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>2.532</t>
+          <t>2971410.24111762</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2.836</t>
+          <t>3328075.76502697</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2.932</t>
+          <t>3441069.4918347</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>3.031</t>
+          <t>3556965.5773628</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -7898,137 +7903,137 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>0.784</t>
+          <t>927171.471369134</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>0.897</t>
+          <t>1060382.4283977</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.029</t>
+          <t>1216578.66381858</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1.025</t>
+          <t>1211720.46859424</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>1.138</t>
+          <t>1345646.26741676</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>1.492</t>
+          <t>1764921.08356962</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>1.574</t>
+          <t>1861668.8074637</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1.535</t>
+          <t>1815695.13993229</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>1.355</t>
+          <t>1602488.43833072</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>1.453</t>
+          <t>1718442.32556649</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>1.754</t>
+          <t>2074870.85044044</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>2.044</t>
+          <t>2417327.78295331</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>2.275</t>
+          <t>2691088.33399205</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>2.628</t>
+          <t>3108254.54895304</t>
         </is>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2.535</t>
+          <t>2998512.84610092</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>3.088</t>
+          <t>3651851.18284709</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>3.629</t>
+          <t>4291708.08849593</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>4.147</t>
+          <t>4904685.39281939</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>4.005</t>
+          <t>4737094.04851311</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
         <is>
-          <t>3.951</t>
+          <t>4672524.39698447</t>
         </is>
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>4.253</t>
+          <t>5030101.57613283</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>4.298</t>
+          <t>5083182.66411794</t>
         </is>
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>4.434</t>
+          <t>5244465.09462974</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>4.616</t>
+          <t>5459209.94288293</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>5.057</t>
+          <t>5980382.04561112</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>5.341</t>
+          <t>6317059.74301751</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>5.442</t>
+          <t>6436101.819544</t>
         </is>
       </c>
     </row>
@@ -8070,6 +8075,11 @@
           <t>gross_output.s.us</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8104,6 +8114,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Standard v0.9</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>EXI382</t>
